--- a/templates/PTW_Registry_Template_KKS.xlsx
+++ b/templates/PTW_Registry_Template_KKS.xlsx
@@ -853,7 +853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ204"/>
+  <dimension ref="A1:AS204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -899,6 +899,8 @@
     <col width="26" customWidth="1" min="41" max="41"/>
     <col width="26" customWidth="1" min="42" max="42"/>
     <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1117,6 +1119,16 @@
           <t>workParty</t>
         </is>
       </c>
+      <c r="AR1" s="6" t="inlineStr">
+        <is>
+          <t>fireWatcher</t>
+        </is>
+      </c>
+      <c r="AS1" s="6" t="inlineStr">
+        <is>
+          <t>isoNote</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -1129,32 +1141,11 @@
           <t>TYPE OF WORK  /  JENIS PEKERJAAN  (Y = yes)</t>
         </is>
       </c>
-      <c r="K2" s="9" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="M2" s="9" t="n"/>
-      <c r="N2" s="9" t="n"/>
-      <c r="O2" s="9" t="n"/>
-      <c r="P2" s="9" t="n"/>
-      <c r="Q2" s="9" t="n"/>
-      <c r="R2" s="9" t="n"/>
-      <c r="S2" s="9" t="n"/>
-      <c r="T2" s="9" t="n"/>
       <c r="V2" s="8" t="inlineStr">
         <is>
           <t>SUPPORTING DOCUMENTS  /  DOKUMEN PENDUKUNG  (Y = attached)</t>
         </is>
       </c>
-      <c r="W2" s="9" t="n"/>
-      <c r="X2" s="9" t="n"/>
-      <c r="Y2" s="9" t="n"/>
-      <c r="Z2" s="9" t="n"/>
-      <c r="AA2" s="9" t="n"/>
-      <c r="AB2" s="9" t="n"/>
-      <c r="AC2" s="9" t="n"/>
-      <c r="AD2" s="9" t="n"/>
-      <c r="AE2" s="9" t="n"/>
-      <c r="AF2" s="9" t="n"/>
-      <c r="AG2" s="9" t="n"/>
     </row>
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -1415,6 +1406,18 @@
         <is>
           <t>Work party (no. of people)
 Jumlah pekerja</t>
+        </is>
+      </c>
+      <c r="AR3" s="11" t="inlineStr">
+        <is>
+          <t>Fire Watcher name (required if Hot Work)
+Nama Fire Watcher (wajib jika Kerja Panas)</t>
+        </is>
+      </c>
+      <c r="AS3" s="11" t="inlineStr">
+        <is>
+          <t>Isolation not required – reason, by Job Coordinator (needed if Electrical and no Isolation Plan)
+Isolasi tidak diperlukan – alasan oleh Job Coordinator (wajib jika Kelistrikan tanpa Rencana Isolasi)</t>
         </is>
       </c>
     </row>
@@ -1550,6 +1553,12 @@
           <t>6</t>
         </is>
       </c>
+      <c r="AR4" s="13" t="inlineStr">
+        <is>
+          <t>Budi</t>
+        </is>
+      </c>
+      <c r="AS4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="n"/>
@@ -1607,6 +1616,8 @@
       <c r="AO5" s="15" t="n"/>
       <c r="AP5" s="15" t="n"/>
       <c r="AQ5" s="17" t="n"/>
+      <c r="AR5" s="17" t="n"/>
+      <c r="AS5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="n"/>
@@ -1664,6 +1675,8 @@
       <c r="AO6" s="15" t="n"/>
       <c r="AP6" s="15" t="n"/>
       <c r="AQ6" s="17" t="n"/>
+      <c r="AR6" s="17" t="n"/>
+      <c r="AS6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="n"/>
@@ -1721,6 +1734,8 @@
       <c r="AO7" s="15" t="n"/>
       <c r="AP7" s="15" t="n"/>
       <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n"/>
@@ -1778,6 +1793,8 @@
       <c r="AO8" s="15" t="n"/>
       <c r="AP8" s="15" t="n"/>
       <c r="AQ8" s="17" t="n"/>
+      <c r="AR8" s="17" t="n"/>
+      <c r="AS8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="n"/>
@@ -1835,6 +1852,8 @@
       <c r="AO9" s="15" t="n"/>
       <c r="AP9" s="15" t="n"/>
       <c r="AQ9" s="17" t="n"/>
+      <c r="AR9" s="17" t="n"/>
+      <c r="AS9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="n"/>
@@ -1892,6 +1911,8 @@
       <c r="AO10" s="15" t="n"/>
       <c r="AP10" s="15" t="n"/>
       <c r="AQ10" s="17" t="n"/>
+      <c r="AR10" s="17" t="n"/>
+      <c r="AS10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="n"/>
@@ -1949,6 +1970,8 @@
       <c r="AO11" s="15" t="n"/>
       <c r="AP11" s="15" t="n"/>
       <c r="AQ11" s="17" t="n"/>
+      <c r="AR11" s="17" t="n"/>
+      <c r="AS11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n"/>
@@ -2006,6 +2029,8 @@
       <c r="AO12" s="15" t="n"/>
       <c r="AP12" s="15" t="n"/>
       <c r="AQ12" s="17" t="n"/>
+      <c r="AR12" s="17" t="n"/>
+      <c r="AS12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="n"/>
@@ -2063,6 +2088,8 @@
       <c r="AO13" s="15" t="n"/>
       <c r="AP13" s="15" t="n"/>
       <c r="AQ13" s="17" t="n"/>
+      <c r="AR13" s="17" t="n"/>
+      <c r="AS13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n"/>
@@ -2120,6 +2147,8 @@
       <c r="AO14" s="15" t="n"/>
       <c r="AP14" s="15" t="n"/>
       <c r="AQ14" s="17" t="n"/>
+      <c r="AR14" s="17" t="n"/>
+      <c r="AS14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="n"/>
@@ -2177,6 +2206,8 @@
       <c r="AO15" s="15" t="n"/>
       <c r="AP15" s="15" t="n"/>
       <c r="AQ15" s="17" t="n"/>
+      <c r="AR15" s="17" t="n"/>
+      <c r="AS15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="n"/>
@@ -2234,6 +2265,8 @@
       <c r="AO16" s="15" t="n"/>
       <c r="AP16" s="15" t="n"/>
       <c r="AQ16" s="17" t="n"/>
+      <c r="AR16" s="17" t="n"/>
+      <c r="AS16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="n"/>
@@ -2291,6 +2324,8 @@
       <c r="AO17" s="15" t="n"/>
       <c r="AP17" s="15" t="n"/>
       <c r="AQ17" s="17" t="n"/>
+      <c r="AR17" s="17" t="n"/>
+      <c r="AS17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="n"/>
@@ -2348,6 +2383,8 @@
       <c r="AO18" s="15" t="n"/>
       <c r="AP18" s="15" t="n"/>
       <c r="AQ18" s="17" t="n"/>
+      <c r="AR18" s="17" t="n"/>
+      <c r="AS18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="n"/>
@@ -2405,6 +2442,8 @@
       <c r="AO19" s="15" t="n"/>
       <c r="AP19" s="15" t="n"/>
       <c r="AQ19" s="17" t="n"/>
+      <c r="AR19" s="17" t="n"/>
+      <c r="AS19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="n"/>
@@ -2462,6 +2501,8 @@
       <c r="AO20" s="15" t="n"/>
       <c r="AP20" s="15" t="n"/>
       <c r="AQ20" s="17" t="n"/>
+      <c r="AR20" s="17" t="n"/>
+      <c r="AS20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="n"/>
@@ -2519,6 +2560,8 @@
       <c r="AO21" s="15" t="n"/>
       <c r="AP21" s="15" t="n"/>
       <c r="AQ21" s="17" t="n"/>
+      <c r="AR21" s="17" t="n"/>
+      <c r="AS21" s="17" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="n"/>
@@ -2576,6 +2619,8 @@
       <c r="AO22" s="15" t="n"/>
       <c r="AP22" s="15" t="n"/>
       <c r="AQ22" s="17" t="n"/>
+      <c r="AR22" s="17" t="n"/>
+      <c r="AS22" s="17" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="n"/>
@@ -2633,6 +2678,8 @@
       <c r="AO23" s="15" t="n"/>
       <c r="AP23" s="15" t="n"/>
       <c r="AQ23" s="17" t="n"/>
+      <c r="AR23" s="17" t="n"/>
+      <c r="AS23" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="n"/>
@@ -2690,6 +2737,8 @@
       <c r="AO24" s="15" t="n"/>
       <c r="AP24" s="15" t="n"/>
       <c r="AQ24" s="17" t="n"/>
+      <c r="AR24" s="17" t="n"/>
+      <c r="AS24" s="17" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="n"/>
@@ -2747,6 +2796,8 @@
       <c r="AO25" s="15" t="n"/>
       <c r="AP25" s="15" t="n"/>
       <c r="AQ25" s="17" t="n"/>
+      <c r="AR25" s="17" t="n"/>
+      <c r="AS25" s="17" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="15" t="n"/>
@@ -2804,6 +2855,8 @@
       <c r="AO26" s="15" t="n"/>
       <c r="AP26" s="15" t="n"/>
       <c r="AQ26" s="17" t="n"/>
+      <c r="AR26" s="17" t="n"/>
+      <c r="AS26" s="17" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="n"/>
@@ -2861,6 +2914,8 @@
       <c r="AO27" s="15" t="n"/>
       <c r="AP27" s="15" t="n"/>
       <c r="AQ27" s="17" t="n"/>
+      <c r="AR27" s="17" t="n"/>
+      <c r="AS27" s="17" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="n"/>
@@ -2918,6 +2973,8 @@
       <c r="AO28" s="15" t="n"/>
       <c r="AP28" s="15" t="n"/>
       <c r="AQ28" s="17" t="n"/>
+      <c r="AR28" s="17" t="n"/>
+      <c r="AS28" s="17" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="15" t="n"/>
@@ -2975,6 +3032,8 @@
       <c r="AO29" s="15" t="n"/>
       <c r="AP29" s="15" t="n"/>
       <c r="AQ29" s="17" t="n"/>
+      <c r="AR29" s="17" t="n"/>
+      <c r="AS29" s="17" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="n"/>
@@ -3032,6 +3091,8 @@
       <c r="AO30" s="15" t="n"/>
       <c r="AP30" s="15" t="n"/>
       <c r="AQ30" s="17" t="n"/>
+      <c r="AR30" s="17" t="n"/>
+      <c r="AS30" s="17" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="n"/>
@@ -3089,6 +3150,8 @@
       <c r="AO31" s="15" t="n"/>
       <c r="AP31" s="15" t="n"/>
       <c r="AQ31" s="17" t="n"/>
+      <c r="AR31" s="17" t="n"/>
+      <c r="AS31" s="17" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="n"/>
@@ -3146,6 +3209,8 @@
       <c r="AO32" s="15" t="n"/>
       <c r="AP32" s="15" t="n"/>
       <c r="AQ32" s="17" t="n"/>
+      <c r="AR32" s="17" t="n"/>
+      <c r="AS32" s="17" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="15" t="n"/>
@@ -3203,6 +3268,8 @@
       <c r="AO33" s="15" t="n"/>
       <c r="AP33" s="15" t="n"/>
       <c r="AQ33" s="17" t="n"/>
+      <c r="AR33" s="17" t="n"/>
+      <c r="AS33" s="17" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="15" t="n"/>
@@ -3260,6 +3327,8 @@
       <c r="AO34" s="15" t="n"/>
       <c r="AP34" s="15" t="n"/>
       <c r="AQ34" s="17" t="n"/>
+      <c r="AR34" s="17" t="n"/>
+      <c r="AS34" s="17" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="15" t="n"/>
@@ -3317,6 +3386,8 @@
       <c r="AO35" s="15" t="n"/>
       <c r="AP35" s="15" t="n"/>
       <c r="AQ35" s="17" t="n"/>
+      <c r="AR35" s="17" t="n"/>
+      <c r="AS35" s="17" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="15" t="n"/>
@@ -3374,6 +3445,8 @@
       <c r="AO36" s="15" t="n"/>
       <c r="AP36" s="15" t="n"/>
       <c r="AQ36" s="17" t="n"/>
+      <c r="AR36" s="17" t="n"/>
+      <c r="AS36" s="17" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="n"/>
@@ -3431,6 +3504,8 @@
       <c r="AO37" s="15" t="n"/>
       <c r="AP37" s="15" t="n"/>
       <c r="AQ37" s="17" t="n"/>
+      <c r="AR37" s="17" t="n"/>
+      <c r="AS37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="15" t="n"/>
@@ -3488,6 +3563,8 @@
       <c r="AO38" s="15" t="n"/>
       <c r="AP38" s="15" t="n"/>
       <c r="AQ38" s="17" t="n"/>
+      <c r="AR38" s="17" t="n"/>
+      <c r="AS38" s="17" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="15" t="n"/>
@@ -3545,6 +3622,8 @@
       <c r="AO39" s="15" t="n"/>
       <c r="AP39" s="15" t="n"/>
       <c r="AQ39" s="17" t="n"/>
+      <c r="AR39" s="17" t="n"/>
+      <c r="AS39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="15" t="n"/>
@@ -3602,6 +3681,8 @@
       <c r="AO40" s="15" t="n"/>
       <c r="AP40" s="15" t="n"/>
       <c r="AQ40" s="17" t="n"/>
+      <c r="AR40" s="17" t="n"/>
+      <c r="AS40" s="17" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="15" t="n"/>
@@ -3659,6 +3740,8 @@
       <c r="AO41" s="15" t="n"/>
       <c r="AP41" s="15" t="n"/>
       <c r="AQ41" s="17" t="n"/>
+      <c r="AR41" s="17" t="n"/>
+      <c r="AS41" s="17" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="15" t="n"/>
@@ -3716,6 +3799,8 @@
       <c r="AO42" s="15" t="n"/>
       <c r="AP42" s="15" t="n"/>
       <c r="AQ42" s="17" t="n"/>
+      <c r="AR42" s="17" t="n"/>
+      <c r="AS42" s="17" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="15" t="n"/>
@@ -3773,6 +3858,8 @@
       <c r="AO43" s="15" t="n"/>
       <c r="AP43" s="15" t="n"/>
       <c r="AQ43" s="17" t="n"/>
+      <c r="AR43" s="17" t="n"/>
+      <c r="AS43" s="17" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="15" t="n"/>
@@ -3830,6 +3917,8 @@
       <c r="AO44" s="15" t="n"/>
       <c r="AP44" s="15" t="n"/>
       <c r="AQ44" s="17" t="n"/>
+      <c r="AR44" s="17" t="n"/>
+      <c r="AS44" s="17" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="15" t="n"/>
@@ -3887,6 +3976,8 @@
       <c r="AO45" s="15" t="n"/>
       <c r="AP45" s="15" t="n"/>
       <c r="AQ45" s="17" t="n"/>
+      <c r="AR45" s="17" t="n"/>
+      <c r="AS45" s="17" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="n"/>
@@ -3944,6 +4035,8 @@
       <c r="AO46" s="15" t="n"/>
       <c r="AP46" s="15" t="n"/>
       <c r="AQ46" s="17" t="n"/>
+      <c r="AR46" s="17" t="n"/>
+      <c r="AS46" s="17" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="15" t="n"/>
@@ -4001,6 +4094,8 @@
       <c r="AO47" s="15" t="n"/>
       <c r="AP47" s="15" t="n"/>
       <c r="AQ47" s="17" t="n"/>
+      <c r="AR47" s="17" t="n"/>
+      <c r="AS47" s="17" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="15" t="n"/>
@@ -4058,6 +4153,8 @@
       <c r="AO48" s="15" t="n"/>
       <c r="AP48" s="15" t="n"/>
       <c r="AQ48" s="17" t="n"/>
+      <c r="AR48" s="17" t="n"/>
+      <c r="AS48" s="17" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="15" t="n"/>
@@ -4115,6 +4212,8 @@
       <c r="AO49" s="15" t="n"/>
       <c r="AP49" s="15" t="n"/>
       <c r="AQ49" s="17" t="n"/>
+      <c r="AR49" s="17" t="n"/>
+      <c r="AS49" s="17" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="15" t="n"/>
@@ -4172,6 +4271,8 @@
       <c r="AO50" s="15" t="n"/>
       <c r="AP50" s="15" t="n"/>
       <c r="AQ50" s="17" t="n"/>
+      <c r="AR50" s="17" t="n"/>
+      <c r="AS50" s="17" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="15" t="n"/>
@@ -4229,6 +4330,8 @@
       <c r="AO51" s="15" t="n"/>
       <c r="AP51" s="15" t="n"/>
       <c r="AQ51" s="17" t="n"/>
+      <c r="AR51" s="17" t="n"/>
+      <c r="AS51" s="17" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="15" t="n"/>
@@ -4286,6 +4389,8 @@
       <c r="AO52" s="15" t="n"/>
       <c r="AP52" s="15" t="n"/>
       <c r="AQ52" s="17" t="n"/>
+      <c r="AR52" s="17" t="n"/>
+      <c r="AS52" s="17" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="15" t="n"/>
@@ -4343,6 +4448,8 @@
       <c r="AO53" s="15" t="n"/>
       <c r="AP53" s="15" t="n"/>
       <c r="AQ53" s="17" t="n"/>
+      <c r="AR53" s="17" t="n"/>
+      <c r="AS53" s="17" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="15" t="n"/>
@@ -4400,6 +4507,8 @@
       <c r="AO54" s="15" t="n"/>
       <c r="AP54" s="15" t="n"/>
       <c r="AQ54" s="17" t="n"/>
+      <c r="AR54" s="17" t="n"/>
+      <c r="AS54" s="17" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="15" t="n"/>
@@ -4457,6 +4566,8 @@
       <c r="AO55" s="15" t="n"/>
       <c r="AP55" s="15" t="n"/>
       <c r="AQ55" s="17" t="n"/>
+      <c r="AR55" s="17" t="n"/>
+      <c r="AS55" s="17" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="15" t="n"/>
@@ -4514,6 +4625,8 @@
       <c r="AO56" s="15" t="n"/>
       <c r="AP56" s="15" t="n"/>
       <c r="AQ56" s="17" t="n"/>
+      <c r="AR56" s="17" t="n"/>
+      <c r="AS56" s="17" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="15" t="n"/>
@@ -4571,6 +4684,8 @@
       <c r="AO57" s="15" t="n"/>
       <c r="AP57" s="15" t="n"/>
       <c r="AQ57" s="17" t="n"/>
+      <c r="AR57" s="17" t="n"/>
+      <c r="AS57" s="17" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="15" t="n"/>
@@ -4628,6 +4743,8 @@
       <c r="AO58" s="15" t="n"/>
       <c r="AP58" s="15" t="n"/>
       <c r="AQ58" s="17" t="n"/>
+      <c r="AR58" s="17" t="n"/>
+      <c r="AS58" s="17" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="15" t="n"/>
@@ -4685,6 +4802,8 @@
       <c r="AO59" s="15" t="n"/>
       <c r="AP59" s="15" t="n"/>
       <c r="AQ59" s="17" t="n"/>
+      <c r="AR59" s="17" t="n"/>
+      <c r="AS59" s="17" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="15" t="n"/>
@@ -4742,6 +4861,8 @@
       <c r="AO60" s="15" t="n"/>
       <c r="AP60" s="15" t="n"/>
       <c r="AQ60" s="17" t="n"/>
+      <c r="AR60" s="17" t="n"/>
+      <c r="AS60" s="17" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="15" t="n"/>
@@ -4799,6 +4920,8 @@
       <c r="AO61" s="15" t="n"/>
       <c r="AP61" s="15" t="n"/>
       <c r="AQ61" s="17" t="n"/>
+      <c r="AR61" s="17" t="n"/>
+      <c r="AS61" s="17" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="15" t="n"/>
@@ -4856,6 +4979,8 @@
       <c r="AO62" s="15" t="n"/>
       <c r="AP62" s="15" t="n"/>
       <c r="AQ62" s="17" t="n"/>
+      <c r="AR62" s="17" t="n"/>
+      <c r="AS62" s="17" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="15" t="n"/>
@@ -4913,6 +5038,8 @@
       <c r="AO63" s="15" t="n"/>
       <c r="AP63" s="15" t="n"/>
       <c r="AQ63" s="17" t="n"/>
+      <c r="AR63" s="17" t="n"/>
+      <c r="AS63" s="17" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="15" t="n"/>
@@ -4970,6 +5097,8 @@
       <c r="AO64" s="15" t="n"/>
       <c r="AP64" s="15" t="n"/>
       <c r="AQ64" s="17" t="n"/>
+      <c r="AR64" s="17" t="n"/>
+      <c r="AS64" s="17" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="15" t="n"/>
@@ -5027,6 +5156,8 @@
       <c r="AO65" s="15" t="n"/>
       <c r="AP65" s="15" t="n"/>
       <c r="AQ65" s="17" t="n"/>
+      <c r="AR65" s="17" t="n"/>
+      <c r="AS65" s="17" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="15" t="n"/>
@@ -5084,6 +5215,8 @@
       <c r="AO66" s="15" t="n"/>
       <c r="AP66" s="15" t="n"/>
       <c r="AQ66" s="17" t="n"/>
+      <c r="AR66" s="17" t="n"/>
+      <c r="AS66" s="17" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="15" t="n"/>
@@ -5141,6 +5274,8 @@
       <c r="AO67" s="15" t="n"/>
       <c r="AP67" s="15" t="n"/>
       <c r="AQ67" s="17" t="n"/>
+      <c r="AR67" s="17" t="n"/>
+      <c r="AS67" s="17" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="15" t="n"/>
@@ -5198,6 +5333,8 @@
       <c r="AO68" s="15" t="n"/>
       <c r="AP68" s="15" t="n"/>
       <c r="AQ68" s="17" t="n"/>
+      <c r="AR68" s="17" t="n"/>
+      <c r="AS68" s="17" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="15" t="n"/>
@@ -5255,6 +5392,8 @@
       <c r="AO69" s="15" t="n"/>
       <c r="AP69" s="15" t="n"/>
       <c r="AQ69" s="17" t="n"/>
+      <c r="AR69" s="17" t="n"/>
+      <c r="AS69" s="17" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="15" t="n"/>
@@ -5312,6 +5451,8 @@
       <c r="AO70" s="15" t="n"/>
       <c r="AP70" s="15" t="n"/>
       <c r="AQ70" s="17" t="n"/>
+      <c r="AR70" s="17" t="n"/>
+      <c r="AS70" s="17" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="15" t="n"/>
@@ -5369,6 +5510,8 @@
       <c r="AO71" s="15" t="n"/>
       <c r="AP71" s="15" t="n"/>
       <c r="AQ71" s="17" t="n"/>
+      <c r="AR71" s="17" t="n"/>
+      <c r="AS71" s="17" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="15" t="n"/>
@@ -5426,6 +5569,8 @@
       <c r="AO72" s="15" t="n"/>
       <c r="AP72" s="15" t="n"/>
       <c r="AQ72" s="17" t="n"/>
+      <c r="AR72" s="17" t="n"/>
+      <c r="AS72" s="17" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="15" t="n"/>
@@ -5483,6 +5628,8 @@
       <c r="AO73" s="15" t="n"/>
       <c r="AP73" s="15" t="n"/>
       <c r="AQ73" s="17" t="n"/>
+      <c r="AR73" s="17" t="n"/>
+      <c r="AS73" s="17" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="15" t="n"/>
@@ -5540,6 +5687,8 @@
       <c r="AO74" s="15" t="n"/>
       <c r="AP74" s="15" t="n"/>
       <c r="AQ74" s="17" t="n"/>
+      <c r="AR74" s="17" t="n"/>
+      <c r="AS74" s="17" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="15" t="n"/>
@@ -5597,6 +5746,8 @@
       <c r="AO75" s="15" t="n"/>
       <c r="AP75" s="15" t="n"/>
       <c r="AQ75" s="17" t="n"/>
+      <c r="AR75" s="17" t="n"/>
+      <c r="AS75" s="17" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="15" t="n"/>
@@ -5654,6 +5805,8 @@
       <c r="AO76" s="15" t="n"/>
       <c r="AP76" s="15" t="n"/>
       <c r="AQ76" s="17" t="n"/>
+      <c r="AR76" s="17" t="n"/>
+      <c r="AS76" s="17" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="15" t="n"/>
@@ -5711,6 +5864,8 @@
       <c r="AO77" s="15" t="n"/>
       <c r="AP77" s="15" t="n"/>
       <c r="AQ77" s="17" t="n"/>
+      <c r="AR77" s="17" t="n"/>
+      <c r="AS77" s="17" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="15" t="n"/>
@@ -5768,6 +5923,8 @@
       <c r="AO78" s="15" t="n"/>
       <c r="AP78" s="15" t="n"/>
       <c r="AQ78" s="17" t="n"/>
+      <c r="AR78" s="17" t="n"/>
+      <c r="AS78" s="17" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="15" t="n"/>
@@ -5825,6 +5982,8 @@
       <c r="AO79" s="15" t="n"/>
       <c r="AP79" s="15" t="n"/>
       <c r="AQ79" s="17" t="n"/>
+      <c r="AR79" s="17" t="n"/>
+      <c r="AS79" s="17" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="15" t="n"/>
@@ -5882,6 +6041,8 @@
       <c r="AO80" s="15" t="n"/>
       <c r="AP80" s="15" t="n"/>
       <c r="AQ80" s="17" t="n"/>
+      <c r="AR80" s="17" t="n"/>
+      <c r="AS80" s="17" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="15" t="n"/>
@@ -5939,6 +6100,8 @@
       <c r="AO81" s="15" t="n"/>
       <c r="AP81" s="15" t="n"/>
       <c r="AQ81" s="17" t="n"/>
+      <c r="AR81" s="17" t="n"/>
+      <c r="AS81" s="17" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="15" t="n"/>
@@ -5996,6 +6159,8 @@
       <c r="AO82" s="15" t="n"/>
       <c r="AP82" s="15" t="n"/>
       <c r="AQ82" s="17" t="n"/>
+      <c r="AR82" s="17" t="n"/>
+      <c r="AS82" s="17" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="15" t="n"/>
@@ -6053,6 +6218,8 @@
       <c r="AO83" s="15" t="n"/>
       <c r="AP83" s="15" t="n"/>
       <c r="AQ83" s="17" t="n"/>
+      <c r="AR83" s="17" t="n"/>
+      <c r="AS83" s="17" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="15" t="n"/>
@@ -6110,6 +6277,8 @@
       <c r="AO84" s="15" t="n"/>
       <c r="AP84" s="15" t="n"/>
       <c r="AQ84" s="17" t="n"/>
+      <c r="AR84" s="17" t="n"/>
+      <c r="AS84" s="17" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="15" t="n"/>
@@ -6167,6 +6336,8 @@
       <c r="AO85" s="15" t="n"/>
       <c r="AP85" s="15" t="n"/>
       <c r="AQ85" s="17" t="n"/>
+      <c r="AR85" s="17" t="n"/>
+      <c r="AS85" s="17" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="15" t="n"/>
@@ -6224,6 +6395,8 @@
       <c r="AO86" s="15" t="n"/>
       <c r="AP86" s="15" t="n"/>
       <c r="AQ86" s="17" t="n"/>
+      <c r="AR86" s="17" t="n"/>
+      <c r="AS86" s="17" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="15" t="n"/>
@@ -6281,6 +6454,8 @@
       <c r="AO87" s="15" t="n"/>
       <c r="AP87" s="15" t="n"/>
       <c r="AQ87" s="17" t="n"/>
+      <c r="AR87" s="17" t="n"/>
+      <c r="AS87" s="17" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="15" t="n"/>
@@ -6338,6 +6513,8 @@
       <c r="AO88" s="15" t="n"/>
       <c r="AP88" s="15" t="n"/>
       <c r="AQ88" s="17" t="n"/>
+      <c r="AR88" s="17" t="n"/>
+      <c r="AS88" s="17" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="15" t="n"/>
@@ -6395,6 +6572,8 @@
       <c r="AO89" s="15" t="n"/>
       <c r="AP89" s="15" t="n"/>
       <c r="AQ89" s="17" t="n"/>
+      <c r="AR89" s="17" t="n"/>
+      <c r="AS89" s="17" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="15" t="n"/>
@@ -6452,6 +6631,8 @@
       <c r="AO90" s="15" t="n"/>
       <c r="AP90" s="15" t="n"/>
       <c r="AQ90" s="17" t="n"/>
+      <c r="AR90" s="17" t="n"/>
+      <c r="AS90" s="17" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="15" t="n"/>
@@ -6509,6 +6690,8 @@
       <c r="AO91" s="15" t="n"/>
       <c r="AP91" s="15" t="n"/>
       <c r="AQ91" s="17" t="n"/>
+      <c r="AR91" s="17" t="n"/>
+      <c r="AS91" s="17" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="15" t="n"/>
@@ -6566,6 +6749,8 @@
       <c r="AO92" s="15" t="n"/>
       <c r="AP92" s="15" t="n"/>
       <c r="AQ92" s="17" t="n"/>
+      <c r="AR92" s="17" t="n"/>
+      <c r="AS92" s="17" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="15" t="n"/>
@@ -6623,6 +6808,8 @@
       <c r="AO93" s="15" t="n"/>
       <c r="AP93" s="15" t="n"/>
       <c r="AQ93" s="17" t="n"/>
+      <c r="AR93" s="17" t="n"/>
+      <c r="AS93" s="17" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="15" t="n"/>
@@ -6680,6 +6867,8 @@
       <c r="AO94" s="15" t="n"/>
       <c r="AP94" s="15" t="n"/>
       <c r="AQ94" s="17" t="n"/>
+      <c r="AR94" s="17" t="n"/>
+      <c r="AS94" s="17" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="15" t="n"/>
@@ -6737,6 +6926,8 @@
       <c r="AO95" s="15" t="n"/>
       <c r="AP95" s="15" t="n"/>
       <c r="AQ95" s="17" t="n"/>
+      <c r="AR95" s="17" t="n"/>
+      <c r="AS95" s="17" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="15" t="n"/>
@@ -6794,6 +6985,8 @@
       <c r="AO96" s="15" t="n"/>
       <c r="AP96" s="15" t="n"/>
       <c r="AQ96" s="17" t="n"/>
+      <c r="AR96" s="17" t="n"/>
+      <c r="AS96" s="17" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="15" t="n"/>
@@ -6851,6 +7044,8 @@
       <c r="AO97" s="15" t="n"/>
       <c r="AP97" s="15" t="n"/>
       <c r="AQ97" s="17" t="n"/>
+      <c r="AR97" s="17" t="n"/>
+      <c r="AS97" s="17" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="15" t="n"/>
@@ -6908,6 +7103,8 @@
       <c r="AO98" s="15" t="n"/>
       <c r="AP98" s="15" t="n"/>
       <c r="AQ98" s="17" t="n"/>
+      <c r="AR98" s="17" t="n"/>
+      <c r="AS98" s="17" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="15" t="n"/>
@@ -6965,6 +7162,8 @@
       <c r="AO99" s="15" t="n"/>
       <c r="AP99" s="15" t="n"/>
       <c r="AQ99" s="17" t="n"/>
+      <c r="AR99" s="17" t="n"/>
+      <c r="AS99" s="17" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="15" t="n"/>
@@ -7022,6 +7221,8 @@
       <c r="AO100" s="15" t="n"/>
       <c r="AP100" s="15" t="n"/>
       <c r="AQ100" s="17" t="n"/>
+      <c r="AR100" s="17" t="n"/>
+      <c r="AS100" s="17" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="15" t="n"/>
@@ -7079,6 +7280,8 @@
       <c r="AO101" s="15" t="n"/>
       <c r="AP101" s="15" t="n"/>
       <c r="AQ101" s="17" t="n"/>
+      <c r="AR101" s="17" t="n"/>
+      <c r="AS101" s="17" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="15" t="n"/>
@@ -7136,6 +7339,8 @@
       <c r="AO102" s="15" t="n"/>
       <c r="AP102" s="15" t="n"/>
       <c r="AQ102" s="17" t="n"/>
+      <c r="AR102" s="17" t="n"/>
+      <c r="AS102" s="17" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="15" t="n"/>
@@ -7193,6 +7398,8 @@
       <c r="AO103" s="15" t="n"/>
       <c r="AP103" s="15" t="n"/>
       <c r="AQ103" s="17" t="n"/>
+      <c r="AR103" s="17" t="n"/>
+      <c r="AS103" s="17" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="15" t="n"/>
@@ -7250,6 +7457,8 @@
       <c r="AO104" s="15" t="n"/>
       <c r="AP104" s="15" t="n"/>
       <c r="AQ104" s="17" t="n"/>
+      <c r="AR104" s="17" t="n"/>
+      <c r="AS104" s="17" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="15" t="n"/>
@@ -7307,6 +7516,8 @@
       <c r="AO105" s="15" t="n"/>
       <c r="AP105" s="15" t="n"/>
       <c r="AQ105" s="17" t="n"/>
+      <c r="AR105" s="17" t="n"/>
+      <c r="AS105" s="17" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="15" t="n"/>
@@ -7364,6 +7575,8 @@
       <c r="AO106" s="15" t="n"/>
       <c r="AP106" s="15" t="n"/>
       <c r="AQ106" s="17" t="n"/>
+      <c r="AR106" s="17" t="n"/>
+      <c r="AS106" s="17" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="15" t="n"/>
@@ -7421,6 +7634,8 @@
       <c r="AO107" s="15" t="n"/>
       <c r="AP107" s="15" t="n"/>
       <c r="AQ107" s="17" t="n"/>
+      <c r="AR107" s="17" t="n"/>
+      <c r="AS107" s="17" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="15" t="n"/>
@@ -7478,6 +7693,8 @@
       <c r="AO108" s="15" t="n"/>
       <c r="AP108" s="15" t="n"/>
       <c r="AQ108" s="17" t="n"/>
+      <c r="AR108" s="17" t="n"/>
+      <c r="AS108" s="17" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="15" t="n"/>
@@ -7535,6 +7752,8 @@
       <c r="AO109" s="15" t="n"/>
       <c r="AP109" s="15" t="n"/>
       <c r="AQ109" s="17" t="n"/>
+      <c r="AR109" s="17" t="n"/>
+      <c r="AS109" s="17" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="15" t="n"/>
@@ -7592,6 +7811,8 @@
       <c r="AO110" s="15" t="n"/>
       <c r="AP110" s="15" t="n"/>
       <c r="AQ110" s="17" t="n"/>
+      <c r="AR110" s="17" t="n"/>
+      <c r="AS110" s="17" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="15" t="n"/>
@@ -7649,6 +7870,8 @@
       <c r="AO111" s="15" t="n"/>
       <c r="AP111" s="15" t="n"/>
       <c r="AQ111" s="17" t="n"/>
+      <c r="AR111" s="17" t="n"/>
+      <c r="AS111" s="17" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="15" t="n"/>
@@ -7706,6 +7929,8 @@
       <c r="AO112" s="15" t="n"/>
       <c r="AP112" s="15" t="n"/>
       <c r="AQ112" s="17" t="n"/>
+      <c r="AR112" s="17" t="n"/>
+      <c r="AS112" s="17" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="15" t="n"/>
@@ -7763,6 +7988,8 @@
       <c r="AO113" s="15" t="n"/>
       <c r="AP113" s="15" t="n"/>
       <c r="AQ113" s="17" t="n"/>
+      <c r="AR113" s="17" t="n"/>
+      <c r="AS113" s="17" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="15" t="n"/>
@@ -7820,6 +8047,8 @@
       <c r="AO114" s="15" t="n"/>
       <c r="AP114" s="15" t="n"/>
       <c r="AQ114" s="17" t="n"/>
+      <c r="AR114" s="17" t="n"/>
+      <c r="AS114" s="17" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="15" t="n"/>
@@ -7877,6 +8106,8 @@
       <c r="AO115" s="15" t="n"/>
       <c r="AP115" s="15" t="n"/>
       <c r="AQ115" s="17" t="n"/>
+      <c r="AR115" s="17" t="n"/>
+      <c r="AS115" s="17" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="15" t="n"/>
@@ -7934,6 +8165,8 @@
       <c r="AO116" s="15" t="n"/>
       <c r="AP116" s="15" t="n"/>
       <c r="AQ116" s="17" t="n"/>
+      <c r="AR116" s="17" t="n"/>
+      <c r="AS116" s="17" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="15" t="n"/>
@@ -7991,6 +8224,8 @@
       <c r="AO117" s="15" t="n"/>
       <c r="AP117" s="15" t="n"/>
       <c r="AQ117" s="17" t="n"/>
+      <c r="AR117" s="17" t="n"/>
+      <c r="AS117" s="17" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="15" t="n"/>
@@ -8048,6 +8283,8 @@
       <c r="AO118" s="15" t="n"/>
       <c r="AP118" s="15" t="n"/>
       <c r="AQ118" s="17" t="n"/>
+      <c r="AR118" s="17" t="n"/>
+      <c r="AS118" s="17" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="15" t="n"/>
@@ -8105,6 +8342,8 @@
       <c r="AO119" s="15" t="n"/>
       <c r="AP119" s="15" t="n"/>
       <c r="AQ119" s="17" t="n"/>
+      <c r="AR119" s="17" t="n"/>
+      <c r="AS119" s="17" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="15" t="n"/>
@@ -8162,6 +8401,8 @@
       <c r="AO120" s="15" t="n"/>
       <c r="AP120" s="15" t="n"/>
       <c r="AQ120" s="17" t="n"/>
+      <c r="AR120" s="17" t="n"/>
+      <c r="AS120" s="17" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="15" t="n"/>
@@ -8219,6 +8460,8 @@
       <c r="AO121" s="15" t="n"/>
       <c r="AP121" s="15" t="n"/>
       <c r="AQ121" s="17" t="n"/>
+      <c r="AR121" s="17" t="n"/>
+      <c r="AS121" s="17" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="15" t="n"/>
@@ -8276,6 +8519,8 @@
       <c r="AO122" s="15" t="n"/>
       <c r="AP122" s="15" t="n"/>
       <c r="AQ122" s="17" t="n"/>
+      <c r="AR122" s="17" t="n"/>
+      <c r="AS122" s="17" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="15" t="n"/>
@@ -8333,6 +8578,8 @@
       <c r="AO123" s="15" t="n"/>
       <c r="AP123" s="15" t="n"/>
       <c r="AQ123" s="17" t="n"/>
+      <c r="AR123" s="17" t="n"/>
+      <c r="AS123" s="17" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="15" t="n"/>
@@ -8390,6 +8637,8 @@
       <c r="AO124" s="15" t="n"/>
       <c r="AP124" s="15" t="n"/>
       <c r="AQ124" s="17" t="n"/>
+      <c r="AR124" s="17" t="n"/>
+      <c r="AS124" s="17" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="15" t="n"/>
@@ -8447,6 +8696,8 @@
       <c r="AO125" s="15" t="n"/>
       <c r="AP125" s="15" t="n"/>
       <c r="AQ125" s="17" t="n"/>
+      <c r="AR125" s="17" t="n"/>
+      <c r="AS125" s="17" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="15" t="n"/>
@@ -8504,6 +8755,8 @@
       <c r="AO126" s="15" t="n"/>
       <c r="AP126" s="15" t="n"/>
       <c r="AQ126" s="17" t="n"/>
+      <c r="AR126" s="17" t="n"/>
+      <c r="AS126" s="17" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="15" t="n"/>
@@ -8561,6 +8814,8 @@
       <c r="AO127" s="15" t="n"/>
       <c r="AP127" s="15" t="n"/>
       <c r="AQ127" s="17" t="n"/>
+      <c r="AR127" s="17" t="n"/>
+      <c r="AS127" s="17" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="15" t="n"/>
@@ -8618,6 +8873,8 @@
       <c r="AO128" s="15" t="n"/>
       <c r="AP128" s="15" t="n"/>
       <c r="AQ128" s="17" t="n"/>
+      <c r="AR128" s="17" t="n"/>
+      <c r="AS128" s="17" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="15" t="n"/>
@@ -8675,6 +8932,8 @@
       <c r="AO129" s="15" t="n"/>
       <c r="AP129" s="15" t="n"/>
       <c r="AQ129" s="17" t="n"/>
+      <c r="AR129" s="17" t="n"/>
+      <c r="AS129" s="17" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="15" t="n"/>
@@ -8732,6 +8991,8 @@
       <c r="AO130" s="15" t="n"/>
       <c r="AP130" s="15" t="n"/>
       <c r="AQ130" s="17" t="n"/>
+      <c r="AR130" s="17" t="n"/>
+      <c r="AS130" s="17" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="15" t="n"/>
@@ -8789,6 +9050,8 @@
       <c r="AO131" s="15" t="n"/>
       <c r="AP131" s="15" t="n"/>
       <c r="AQ131" s="17" t="n"/>
+      <c r="AR131" s="17" t="n"/>
+      <c r="AS131" s="17" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="15" t="n"/>
@@ -8846,6 +9109,8 @@
       <c r="AO132" s="15" t="n"/>
       <c r="AP132" s="15" t="n"/>
       <c r="AQ132" s="17" t="n"/>
+      <c r="AR132" s="17" t="n"/>
+      <c r="AS132" s="17" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="15" t="n"/>
@@ -8903,6 +9168,8 @@
       <c r="AO133" s="15" t="n"/>
       <c r="AP133" s="15" t="n"/>
       <c r="AQ133" s="17" t="n"/>
+      <c r="AR133" s="17" t="n"/>
+      <c r="AS133" s="17" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="15" t="n"/>
@@ -8960,6 +9227,8 @@
       <c r="AO134" s="15" t="n"/>
       <c r="AP134" s="15" t="n"/>
       <c r="AQ134" s="17" t="n"/>
+      <c r="AR134" s="17" t="n"/>
+      <c r="AS134" s="17" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="15" t="n"/>
@@ -9017,6 +9286,8 @@
       <c r="AO135" s="15" t="n"/>
       <c r="AP135" s="15" t="n"/>
       <c r="AQ135" s="17" t="n"/>
+      <c r="AR135" s="17" t="n"/>
+      <c r="AS135" s="17" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="15" t="n"/>
@@ -9074,6 +9345,8 @@
       <c r="AO136" s="15" t="n"/>
       <c r="AP136" s="15" t="n"/>
       <c r="AQ136" s="17" t="n"/>
+      <c r="AR136" s="17" t="n"/>
+      <c r="AS136" s="17" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="15" t="n"/>
@@ -9131,6 +9404,8 @@
       <c r="AO137" s="15" t="n"/>
       <c r="AP137" s="15" t="n"/>
       <c r="AQ137" s="17" t="n"/>
+      <c r="AR137" s="17" t="n"/>
+      <c r="AS137" s="17" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="15" t="n"/>
@@ -9188,6 +9463,8 @@
       <c r="AO138" s="15" t="n"/>
       <c r="AP138" s="15" t="n"/>
       <c r="AQ138" s="17" t="n"/>
+      <c r="AR138" s="17" t="n"/>
+      <c r="AS138" s="17" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="15" t="n"/>
@@ -9245,6 +9522,8 @@
       <c r="AO139" s="15" t="n"/>
       <c r="AP139" s="15" t="n"/>
       <c r="AQ139" s="17" t="n"/>
+      <c r="AR139" s="17" t="n"/>
+      <c r="AS139" s="17" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="15" t="n"/>
@@ -9302,6 +9581,8 @@
       <c r="AO140" s="15" t="n"/>
       <c r="AP140" s="15" t="n"/>
       <c r="AQ140" s="17" t="n"/>
+      <c r="AR140" s="17" t="n"/>
+      <c r="AS140" s="17" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="15" t="n"/>
@@ -9359,6 +9640,8 @@
       <c r="AO141" s="15" t="n"/>
       <c r="AP141" s="15" t="n"/>
       <c r="AQ141" s="17" t="n"/>
+      <c r="AR141" s="17" t="n"/>
+      <c r="AS141" s="17" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="15" t="n"/>
@@ -9416,6 +9699,8 @@
       <c r="AO142" s="15" t="n"/>
       <c r="AP142" s="15" t="n"/>
       <c r="AQ142" s="17" t="n"/>
+      <c r="AR142" s="17" t="n"/>
+      <c r="AS142" s="17" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="15" t="n"/>
@@ -9473,6 +9758,8 @@
       <c r="AO143" s="15" t="n"/>
       <c r="AP143" s="15" t="n"/>
       <c r="AQ143" s="17" t="n"/>
+      <c r="AR143" s="17" t="n"/>
+      <c r="AS143" s="17" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="15" t="n"/>
@@ -9530,6 +9817,8 @@
       <c r="AO144" s="15" t="n"/>
       <c r="AP144" s="15" t="n"/>
       <c r="AQ144" s="17" t="n"/>
+      <c r="AR144" s="17" t="n"/>
+      <c r="AS144" s="17" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="15" t="n"/>
@@ -9587,6 +9876,8 @@
       <c r="AO145" s="15" t="n"/>
       <c r="AP145" s="15" t="n"/>
       <c r="AQ145" s="17" t="n"/>
+      <c r="AR145" s="17" t="n"/>
+      <c r="AS145" s="17" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="15" t="n"/>
@@ -9644,6 +9935,8 @@
       <c r="AO146" s="15" t="n"/>
       <c r="AP146" s="15" t="n"/>
       <c r="AQ146" s="17" t="n"/>
+      <c r="AR146" s="17" t="n"/>
+      <c r="AS146" s="17" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="15" t="n"/>
@@ -9701,6 +9994,8 @@
       <c r="AO147" s="15" t="n"/>
       <c r="AP147" s="15" t="n"/>
       <c r="AQ147" s="17" t="n"/>
+      <c r="AR147" s="17" t="n"/>
+      <c r="AS147" s="17" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="15" t="n"/>
@@ -9758,6 +10053,8 @@
       <c r="AO148" s="15" t="n"/>
       <c r="AP148" s="15" t="n"/>
       <c r="AQ148" s="17" t="n"/>
+      <c r="AR148" s="17" t="n"/>
+      <c r="AS148" s="17" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="15" t="n"/>
@@ -9815,6 +10112,8 @@
       <c r="AO149" s="15" t="n"/>
       <c r="AP149" s="15" t="n"/>
       <c r="AQ149" s="17" t="n"/>
+      <c r="AR149" s="17" t="n"/>
+      <c r="AS149" s="17" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="15" t="n"/>
@@ -9872,6 +10171,8 @@
       <c r="AO150" s="15" t="n"/>
       <c r="AP150" s="15" t="n"/>
       <c r="AQ150" s="17" t="n"/>
+      <c r="AR150" s="17" t="n"/>
+      <c r="AS150" s="17" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="15" t="n"/>
@@ -9929,6 +10230,8 @@
       <c r="AO151" s="15" t="n"/>
       <c r="AP151" s="15" t="n"/>
       <c r="AQ151" s="17" t="n"/>
+      <c r="AR151" s="17" t="n"/>
+      <c r="AS151" s="17" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="15" t="n"/>
@@ -9986,6 +10289,8 @@
       <c r="AO152" s="15" t="n"/>
       <c r="AP152" s="15" t="n"/>
       <c r="AQ152" s="17" t="n"/>
+      <c r="AR152" s="17" t="n"/>
+      <c r="AS152" s="17" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="15" t="n"/>
@@ -10043,6 +10348,8 @@
       <c r="AO153" s="15" t="n"/>
       <c r="AP153" s="15" t="n"/>
       <c r="AQ153" s="17" t="n"/>
+      <c r="AR153" s="17" t="n"/>
+      <c r="AS153" s="17" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="15" t="n"/>
@@ -10100,6 +10407,8 @@
       <c r="AO154" s="15" t="n"/>
       <c r="AP154" s="15" t="n"/>
       <c r="AQ154" s="17" t="n"/>
+      <c r="AR154" s="17" t="n"/>
+      <c r="AS154" s="17" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="15" t="n"/>
@@ -10157,6 +10466,8 @@
       <c r="AO155" s="15" t="n"/>
       <c r="AP155" s="15" t="n"/>
       <c r="AQ155" s="17" t="n"/>
+      <c r="AR155" s="17" t="n"/>
+      <c r="AS155" s="17" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="15" t="n"/>
@@ -10214,6 +10525,8 @@
       <c r="AO156" s="15" t="n"/>
       <c r="AP156" s="15" t="n"/>
       <c r="AQ156" s="17" t="n"/>
+      <c r="AR156" s="17" t="n"/>
+      <c r="AS156" s="17" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="15" t="n"/>
@@ -10271,6 +10584,8 @@
       <c r="AO157" s="15" t="n"/>
       <c r="AP157" s="15" t="n"/>
       <c r="AQ157" s="17" t="n"/>
+      <c r="AR157" s="17" t="n"/>
+      <c r="AS157" s="17" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="15" t="n"/>
@@ -10328,6 +10643,8 @@
       <c r="AO158" s="15" t="n"/>
       <c r="AP158" s="15" t="n"/>
       <c r="AQ158" s="17" t="n"/>
+      <c r="AR158" s="17" t="n"/>
+      <c r="AS158" s="17" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="15" t="n"/>
@@ -10385,6 +10702,8 @@
       <c r="AO159" s="15" t="n"/>
       <c r="AP159" s="15" t="n"/>
       <c r="AQ159" s="17" t="n"/>
+      <c r="AR159" s="17" t="n"/>
+      <c r="AS159" s="17" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="15" t="n"/>
@@ -10442,6 +10761,8 @@
       <c r="AO160" s="15" t="n"/>
       <c r="AP160" s="15" t="n"/>
       <c r="AQ160" s="17" t="n"/>
+      <c r="AR160" s="17" t="n"/>
+      <c r="AS160" s="17" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="15" t="n"/>
@@ -10499,6 +10820,8 @@
       <c r="AO161" s="15" t="n"/>
       <c r="AP161" s="15" t="n"/>
       <c r="AQ161" s="17" t="n"/>
+      <c r="AR161" s="17" t="n"/>
+      <c r="AS161" s="17" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="15" t="n"/>
@@ -10556,6 +10879,8 @@
       <c r="AO162" s="15" t="n"/>
       <c r="AP162" s="15" t="n"/>
       <c r="AQ162" s="17" t="n"/>
+      <c r="AR162" s="17" t="n"/>
+      <c r="AS162" s="17" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="15" t="n"/>
@@ -10613,6 +10938,8 @@
       <c r="AO163" s="15" t="n"/>
       <c r="AP163" s="15" t="n"/>
       <c r="AQ163" s="17" t="n"/>
+      <c r="AR163" s="17" t="n"/>
+      <c r="AS163" s="17" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="15" t="n"/>
@@ -10670,6 +10997,8 @@
       <c r="AO164" s="15" t="n"/>
       <c r="AP164" s="15" t="n"/>
       <c r="AQ164" s="17" t="n"/>
+      <c r="AR164" s="17" t="n"/>
+      <c r="AS164" s="17" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="15" t="n"/>
@@ -10727,6 +11056,8 @@
       <c r="AO165" s="15" t="n"/>
       <c r="AP165" s="15" t="n"/>
       <c r="AQ165" s="17" t="n"/>
+      <c r="AR165" s="17" t="n"/>
+      <c r="AS165" s="17" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="15" t="n"/>
@@ -10784,6 +11115,8 @@
       <c r="AO166" s="15" t="n"/>
       <c r="AP166" s="15" t="n"/>
       <c r="AQ166" s="17" t="n"/>
+      <c r="AR166" s="17" t="n"/>
+      <c r="AS166" s="17" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="15" t="n"/>
@@ -10841,6 +11174,8 @@
       <c r="AO167" s="15" t="n"/>
       <c r="AP167" s="15" t="n"/>
       <c r="AQ167" s="17" t="n"/>
+      <c r="AR167" s="17" t="n"/>
+      <c r="AS167" s="17" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="15" t="n"/>
@@ -10898,6 +11233,8 @@
       <c r="AO168" s="15" t="n"/>
       <c r="AP168" s="15" t="n"/>
       <c r="AQ168" s="17" t="n"/>
+      <c r="AR168" s="17" t="n"/>
+      <c r="AS168" s="17" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="15" t="n"/>
@@ -10955,6 +11292,8 @@
       <c r="AO169" s="15" t="n"/>
       <c r="AP169" s="15" t="n"/>
       <c r="AQ169" s="17" t="n"/>
+      <c r="AR169" s="17" t="n"/>
+      <c r="AS169" s="17" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="15" t="n"/>
@@ -11012,6 +11351,8 @@
       <c r="AO170" s="15" t="n"/>
       <c r="AP170" s="15" t="n"/>
       <c r="AQ170" s="17" t="n"/>
+      <c r="AR170" s="17" t="n"/>
+      <c r="AS170" s="17" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="15" t="n"/>
@@ -11069,6 +11410,8 @@
       <c r="AO171" s="15" t="n"/>
       <c r="AP171" s="15" t="n"/>
       <c r="AQ171" s="17" t="n"/>
+      <c r="AR171" s="17" t="n"/>
+      <c r="AS171" s="17" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="15" t="n"/>
@@ -11126,6 +11469,8 @@
       <c r="AO172" s="15" t="n"/>
       <c r="AP172" s="15" t="n"/>
       <c r="AQ172" s="17" t="n"/>
+      <c r="AR172" s="17" t="n"/>
+      <c r="AS172" s="17" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="15" t="n"/>
@@ -11183,6 +11528,8 @@
       <c r="AO173" s="15" t="n"/>
       <c r="AP173" s="15" t="n"/>
       <c r="AQ173" s="17" t="n"/>
+      <c r="AR173" s="17" t="n"/>
+      <c r="AS173" s="17" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="15" t="n"/>
@@ -11240,6 +11587,8 @@
       <c r="AO174" s="15" t="n"/>
       <c r="AP174" s="15" t="n"/>
       <c r="AQ174" s="17" t="n"/>
+      <c r="AR174" s="17" t="n"/>
+      <c r="AS174" s="17" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="15" t="n"/>
@@ -11297,6 +11646,8 @@
       <c r="AO175" s="15" t="n"/>
       <c r="AP175" s="15" t="n"/>
       <c r="AQ175" s="17" t="n"/>
+      <c r="AR175" s="17" t="n"/>
+      <c r="AS175" s="17" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="15" t="n"/>
@@ -11354,6 +11705,8 @@
       <c r="AO176" s="15" t="n"/>
       <c r="AP176" s="15" t="n"/>
       <c r="AQ176" s="17" t="n"/>
+      <c r="AR176" s="17" t="n"/>
+      <c r="AS176" s="17" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="15" t="n"/>
@@ -11411,6 +11764,8 @@
       <c r="AO177" s="15" t="n"/>
       <c r="AP177" s="15" t="n"/>
       <c r="AQ177" s="17" t="n"/>
+      <c r="AR177" s="17" t="n"/>
+      <c r="AS177" s="17" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="15" t="n"/>
@@ -11468,6 +11823,8 @@
       <c r="AO178" s="15" t="n"/>
       <c r="AP178" s="15" t="n"/>
       <c r="AQ178" s="17" t="n"/>
+      <c r="AR178" s="17" t="n"/>
+      <c r="AS178" s="17" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="15" t="n"/>
@@ -11525,6 +11882,8 @@
       <c r="AO179" s="15" t="n"/>
       <c r="AP179" s="15" t="n"/>
       <c r="AQ179" s="17" t="n"/>
+      <c r="AR179" s="17" t="n"/>
+      <c r="AS179" s="17" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="15" t="n"/>
@@ -11582,6 +11941,8 @@
       <c r="AO180" s="15" t="n"/>
       <c r="AP180" s="15" t="n"/>
       <c r="AQ180" s="17" t="n"/>
+      <c r="AR180" s="17" t="n"/>
+      <c r="AS180" s="17" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="15" t="n"/>
@@ -11639,6 +12000,8 @@
       <c r="AO181" s="15" t="n"/>
       <c r="AP181" s="15" t="n"/>
       <c r="AQ181" s="17" t="n"/>
+      <c r="AR181" s="17" t="n"/>
+      <c r="AS181" s="17" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="15" t="n"/>
@@ -11696,6 +12059,8 @@
       <c r="AO182" s="15" t="n"/>
       <c r="AP182" s="15" t="n"/>
       <c r="AQ182" s="17" t="n"/>
+      <c r="AR182" s="17" t="n"/>
+      <c r="AS182" s="17" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="15" t="n"/>
@@ -11753,6 +12118,8 @@
       <c r="AO183" s="15" t="n"/>
       <c r="AP183" s="15" t="n"/>
       <c r="AQ183" s="17" t="n"/>
+      <c r="AR183" s="17" t="n"/>
+      <c r="AS183" s="17" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="15" t="n"/>
@@ -11810,6 +12177,8 @@
       <c r="AO184" s="15" t="n"/>
       <c r="AP184" s="15" t="n"/>
       <c r="AQ184" s="17" t="n"/>
+      <c r="AR184" s="17" t="n"/>
+      <c r="AS184" s="17" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="15" t="n"/>
@@ -11867,6 +12236,8 @@
       <c r="AO185" s="15" t="n"/>
       <c r="AP185" s="15" t="n"/>
       <c r="AQ185" s="17" t="n"/>
+      <c r="AR185" s="17" t="n"/>
+      <c r="AS185" s="17" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="15" t="n"/>
@@ -11924,6 +12295,8 @@
       <c r="AO186" s="15" t="n"/>
       <c r="AP186" s="15" t="n"/>
       <c r="AQ186" s="17" t="n"/>
+      <c r="AR186" s="17" t="n"/>
+      <c r="AS186" s="17" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="15" t="n"/>
@@ -11981,6 +12354,8 @@
       <c r="AO187" s="15" t="n"/>
       <c r="AP187" s="15" t="n"/>
       <c r="AQ187" s="17" t="n"/>
+      <c r="AR187" s="17" t="n"/>
+      <c r="AS187" s="17" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="15" t="n"/>
@@ -12038,6 +12413,8 @@
       <c r="AO188" s="15" t="n"/>
       <c r="AP188" s="15" t="n"/>
       <c r="AQ188" s="17" t="n"/>
+      <c r="AR188" s="17" t="n"/>
+      <c r="AS188" s="17" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="15" t="n"/>
@@ -12095,6 +12472,8 @@
       <c r="AO189" s="15" t="n"/>
       <c r="AP189" s="15" t="n"/>
       <c r="AQ189" s="17" t="n"/>
+      <c r="AR189" s="17" t="n"/>
+      <c r="AS189" s="17" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="15" t="n"/>
@@ -12152,6 +12531,8 @@
       <c r="AO190" s="15" t="n"/>
       <c r="AP190" s="15" t="n"/>
       <c r="AQ190" s="17" t="n"/>
+      <c r="AR190" s="17" t="n"/>
+      <c r="AS190" s="17" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="15" t="n"/>
@@ -12209,6 +12590,8 @@
       <c r="AO191" s="15" t="n"/>
       <c r="AP191" s="15" t="n"/>
       <c r="AQ191" s="17" t="n"/>
+      <c r="AR191" s="17" t="n"/>
+      <c r="AS191" s="17" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="15" t="n"/>
@@ -12266,6 +12649,8 @@
       <c r="AO192" s="15" t="n"/>
       <c r="AP192" s="15" t="n"/>
       <c r="AQ192" s="17" t="n"/>
+      <c r="AR192" s="17" t="n"/>
+      <c r="AS192" s="17" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="15" t="n"/>
@@ -12323,6 +12708,8 @@
       <c r="AO193" s="15" t="n"/>
       <c r="AP193" s="15" t="n"/>
       <c r="AQ193" s="17" t="n"/>
+      <c r="AR193" s="17" t="n"/>
+      <c r="AS193" s="17" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="15" t="n"/>
@@ -12380,6 +12767,8 @@
       <c r="AO194" s="15" t="n"/>
       <c r="AP194" s="15" t="n"/>
       <c r="AQ194" s="17" t="n"/>
+      <c r="AR194" s="17" t="n"/>
+      <c r="AS194" s="17" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="15" t="n"/>
@@ -12437,6 +12826,8 @@
       <c r="AO195" s="15" t="n"/>
       <c r="AP195" s="15" t="n"/>
       <c r="AQ195" s="17" t="n"/>
+      <c r="AR195" s="17" t="n"/>
+      <c r="AS195" s="17" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="15" t="n"/>
@@ -12494,6 +12885,8 @@
       <c r="AO196" s="15" t="n"/>
       <c r="AP196" s="15" t="n"/>
       <c r="AQ196" s="17" t="n"/>
+      <c r="AR196" s="17" t="n"/>
+      <c r="AS196" s="17" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="15" t="n"/>
@@ -12551,6 +12944,8 @@
       <c r="AO197" s="15" t="n"/>
       <c r="AP197" s="15" t="n"/>
       <c r="AQ197" s="17" t="n"/>
+      <c r="AR197" s="17" t="n"/>
+      <c r="AS197" s="17" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="15" t="n"/>
@@ -12608,6 +13003,8 @@
       <c r="AO198" s="15" t="n"/>
       <c r="AP198" s="15" t="n"/>
       <c r="AQ198" s="17" t="n"/>
+      <c r="AR198" s="17" t="n"/>
+      <c r="AS198" s="17" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="15" t="n"/>
@@ -12665,6 +13062,8 @@
       <c r="AO199" s="15" t="n"/>
       <c r="AP199" s="15" t="n"/>
       <c r="AQ199" s="17" t="n"/>
+      <c r="AR199" s="17" t="n"/>
+      <c r="AS199" s="17" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="15" t="n"/>
@@ -12722,6 +13121,8 @@
       <c r="AO200" s="15" t="n"/>
       <c r="AP200" s="15" t="n"/>
       <c r="AQ200" s="17" t="n"/>
+      <c r="AR200" s="17" t="n"/>
+      <c r="AS200" s="17" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="15" t="n"/>
@@ -12779,6 +13180,8 @@
       <c r="AO201" s="15" t="n"/>
       <c r="AP201" s="15" t="n"/>
       <c r="AQ201" s="17" t="n"/>
+      <c r="AR201" s="17" t="n"/>
+      <c r="AS201" s="17" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="15" t="n"/>
@@ -12836,6 +13239,8 @@
       <c r="AO202" s="15" t="n"/>
       <c r="AP202" s="15" t="n"/>
       <c r="AQ202" s="17" t="n"/>
+      <c r="AR202" s="17" t="n"/>
+      <c r="AS202" s="17" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="15" t="n"/>
@@ -12893,6 +13298,8 @@
       <c r="AO203" s="15" t="n"/>
       <c r="AP203" s="15" t="n"/>
       <c r="AQ203" s="17" t="n"/>
+      <c r="AR203" s="17" t="n"/>
+      <c r="AS203" s="17" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="15" t="n"/>
@@ -12950,6 +13357,8 @@
       <c r="AO204" s="15" t="n"/>
       <c r="AP204" s="15" t="n"/>
       <c r="AQ204" s="17" t="n"/>
+      <c r="AR204" s="17" t="n"/>
+      <c r="AS204" s="17" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="E84A"/>
